--- a/data/trans_bre/P6902-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6902-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 39,52</t>
+          <t>-5,63; 42,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 46,46</t>
+          <t>3,45; 46,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 27,56</t>
+          <t>-13,9; 27,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-38,93; 19,91</t>
+          <t>-37,06; 20,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 105,13</t>
+          <t>-9,56; 118,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 108,24</t>
+          <t>7,39; 112,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 63,68</t>
+          <t>-20,57; 60,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,28; 54,14</t>
+          <t>-56,68; 59,88</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 36,92</t>
+          <t>-3,0; 37,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 20,45</t>
+          <t>-26,09; 19,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,16; 50,12</t>
+          <t>15,01; 50,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 34,48</t>
+          <t>-11,0; 34,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 110,82</t>
+          <t>-6,98; 109,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,38; 51,89</t>
+          <t>-45,32; 53,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,97; 252,43</t>
+          <t>41,68; 254,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 119,78</t>
+          <t>-18,48; 133,19</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-44,1; 2,62</t>
+          <t>-44,26; -0,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 49,78</t>
+          <t>-9,46; 47,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 45,5</t>
+          <t>-13,83; 45,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 31,42</t>
+          <t>-5,12; 29,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-89,1; 11,01</t>
+          <t>-88,88; 7,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 277,67</t>
+          <t>-25,17; 284,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-65,02; 779,87</t>
+          <t>-64,66; 818,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 83,63</t>
+          <t>-8,33; 81,45</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 33,54</t>
+          <t>-13,2; 35,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 31,14</t>
+          <t>-15,26; 32,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 9,11</t>
+          <t>-35,72; 11,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-73,63; 4,94</t>
+          <t>-76,21; 7,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 87,67</t>
+          <t>-24,69; 92,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,54; 75,74</t>
+          <t>-24,72; 77,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,53; 12,78</t>
+          <t>-43,39; 16,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,46; 6,95</t>
+          <t>-81,85; 9,92</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 73,59</t>
+          <t>-2,24; 74,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,83; 86,32</t>
+          <t>18,37; 86,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,4; 64,56</t>
+          <t>12,19; 63,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 47,98</t>
+          <t>-5,0; 45,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 490,21</t>
+          <t>-2,94; 481,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,15; 180,93</t>
+          <t>13,86; 172,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 133,04</t>
+          <t>-6,83; 113,59</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 56,01</t>
+          <t>-4,0; 54,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 30,49</t>
+          <t>-22,86; 33,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 58,57</t>
+          <t>-20,21; 62,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 20,43</t>
+          <t>-21,86; 22,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,08; 190,59</t>
+          <t>-6,02; 176,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,22; 75,85</t>
+          <t>-44,32; 88,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-89,81; 475,3</t>
+          <t>-59,47; 500,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 52,14</t>
+          <t>-34,89; 63,57</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 20,15</t>
+          <t>-15,14; 20,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 18,62</t>
+          <t>-22,48; 17,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,89; 45,63</t>
+          <t>8,02; 43,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 23,68</t>
+          <t>-6,41; 21,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 49,55</t>
+          <t>-29,9; 53,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 36,71</t>
+          <t>-32,66; 34,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,78; 145,42</t>
+          <t>14,41; 133,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 42,85</t>
+          <t>-8,46; 38,53</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 20,41</t>
+          <t>-13,54; 20,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 34,26</t>
+          <t>-14,79; 32,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 21,86</t>
+          <t>-30,65; 22,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,91; 10,08</t>
+          <t>-31,83; 9,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 58,93</t>
+          <t>-31,48; 57,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,24; 144,9</t>
+          <t>-37,27; 143,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,26; 50,52</t>
+          <t>-51,32; 60,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 13,3</t>
+          <t>-37,11; 12,45</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 17,13</t>
+          <t>-0,27; 15,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 19,07</t>
+          <t>2,11; 19,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,18; 26,25</t>
+          <t>9,03; 26,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 8,58</t>
+          <t>-19,44; 7,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 43,04</t>
+          <t>-0,43; 39,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,92; 44,65</t>
+          <t>4,33; 45,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,1; 65,36</t>
+          <t>19,68; 65,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 14,38</t>
+          <t>-30,44; 13,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6902-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6902-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-9,34</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-17,29%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 42,13</t>
+          <t>-7,22; 40,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 46,54</t>
+          <t>5,36; 47,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 27,7</t>
+          <t>-13,11; 28,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 20,66</t>
+          <t>-24,59; 27,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 118,14</t>
+          <t>-10,31; 114,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 112,05</t>
+          <t>8,79; 108,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 60,07</t>
+          <t>-19,54; 63,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-56,68; 59,88</t>
+          <t>-48,53; 114,5</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,22</t>
+          <t>9,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 37,26</t>
+          <t>-3,22; 40,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 19,68</t>
+          <t>-26,77; 18,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,01; 50,21</t>
+          <t>15,3; 51,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 34,03</t>
+          <t>-11,64; 31,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 109,06</t>
+          <t>-7,19; 124,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,32; 53,07</t>
+          <t>-46,58; 45,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,68; 254,9</t>
+          <t>44,51; 261,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 133,19</t>
+          <t>-19,19; 101,6</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,1</t>
+          <t>15,56</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-44,26; -0,29</t>
+          <t>-46,41; -1,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 47,15</t>
+          <t>-10,45; 50,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 45,33</t>
+          <t>-16,77; 40,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 29,85</t>
+          <t>-2,27; 34,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-88,88; 7,11</t>
+          <t>-88,44; 7,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 284,04</t>
+          <t>-26,05; 334,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-64,66; 818,47</t>
+          <t>-72,7; 643,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 81,45</t>
+          <t>-3,1; 100,2</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-32,83</t>
+          <t>-6,83</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-42,26%</t>
+          <t>-8,31%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 35,1</t>
+          <t>-12,2; 36,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 32,91</t>
+          <t>-15,87; 31,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,72; 11,19</t>
+          <t>-35,9; 10,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,21; 7,41</t>
+          <t>-23,35; 14,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 92,84</t>
+          <t>-24,2; 102,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 77,93</t>
+          <t>-25,81; 72,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 16,71</t>
+          <t>-43,45; 14,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,85; 9,92</t>
+          <t>-26,07; 21,29</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,81</t>
+          <t>19,59</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 74,81</t>
+          <t>-2,77; 73,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,37; 86,32</t>
+          <t>15,21; 85,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,19; 63,26</t>
+          <t>13,05; 65,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 45,07</t>
+          <t>-8,73; 44,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 481,73</t>
+          <t>1,4; 496,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,86; 172,04</t>
+          <t>15,0; 186,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 113,59</t>
+          <t>-12,13; 110,36</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-0,49%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 54,53</t>
+          <t>-0,48; 54,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 33,15</t>
+          <t>-28,35; 29,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 62,11</t>
+          <t>-21,41; 60,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 22,93</t>
+          <t>-20,67; 21,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 176,75</t>
+          <t>0,96; 176,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,32; 88,35</t>
+          <t>-52,22; 80,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,47; 500,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 63,57</t>
+          <t>-35,16; 59,72</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,6</t>
+          <t>9,76</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 20,97</t>
+          <t>-17,31; 18,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,48; 17,37</t>
+          <t>-22,86; 16,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,02; 43,06</t>
+          <t>8,32; 41,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 21,88</t>
+          <t>-4,06; 23,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 53,75</t>
+          <t>-31,64; 46,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 34,17</t>
+          <t>-34,64; 32,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,41; 133,77</t>
+          <t>20,0; 137,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 38,53</t>
+          <t>-5,53; 43,18</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-6,68</t>
+          <t>-1,84</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-8,43%</t>
+          <t>-2,3%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 20,41</t>
+          <t>-13,81; 19,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 32,76</t>
+          <t>-17,09; 32,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,65; 22,85</t>
+          <t>-32,59; 21,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,83; 9,55</t>
+          <t>-15,38; 12,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,48; 57,11</t>
+          <t>-30,92; 55,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 143,17</t>
+          <t>-41,34; 147,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-51,32; 60,81</t>
+          <t>-54,99; 56,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 12,45</t>
+          <t>-17,84; 17,95</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-2,16%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 15,65</t>
+          <t>-0,25; 15,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,11; 19,13</t>
+          <t>1,2; 18,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,03; 26,24</t>
+          <t>8,58; 25,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 7,81</t>
+          <t>-1,52; 12,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 39,4</t>
+          <t>-0,4; 39,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,33; 45,6</t>
+          <t>2,74; 44,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,68; 65,5</t>
+          <t>18,79; 64,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 13,13</t>
+          <t>-2,22; 23,04</t>
         </is>
       </c>
     </row>
